--- a/tables/supplement_table_mouse_3.xlsx
+++ b/tables/supplement_table_mouse_3.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 - Per-gene summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 - Full GTEx query" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -70,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -80,6 +81,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2812,4 +2816,249 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>accession</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>version_snapshot</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>derived_path_in_repo</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>GTEx Portal v8 eQTL query</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>GTEx Consortium Science 2020</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>v8</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>https://gtexportal.org/home/</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>queried 2026-04 (snapshot)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>results/gtex_eqtl_query_results.csv</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Per (gene × tissue): n_eqtl (significant single-tissue cis-eQTLs at GTEx FDR), best_p, and ad_snp_is_eqtl flag for the Bellenguez 2022 AD GWAS lead SNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Bellenguez 2022 AD GWAS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Bellenguez et al. Nat Genet 2022</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>GCST90027158</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/gwas/studies/GCST90027158</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2022-04 (GRCh38)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>data/gwas/Bellenguez2022_AD_withN.tsv.gz (gitignored)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Used to identify AD GWAS lead SNPs per locus and to test for eQTL overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SMR colocalisation pipeline</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Zhu et al. Nat Genet 2016 (SMR/HEIDI)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://yanglab.westlake.edu.cn/software/smr/</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>v1.3.1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>results/smr_colon_AD_results.csv</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Provides lead_snp (top-eQTL SNP per gene × tissue), n_tested variants, SMR effect size, HEIDI p. Lead-SNP column in this table is sourced here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline notebook</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>This work</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>notebooks/21_eqtl_coloc_analysis.ipynb (also _executed.ipynb)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Runs the GTEx query + SMR for the 10 AD candidate genes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Coloc-ABF + SharePro</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Giambartolomei 2014; Zhang Genome Biol 2023</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/zhwm/SharePro_coloc</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>SharePro v5.0.0</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>results/coloc_FULL_eqtl_results.csv + results/sharepro/{GENE}_v3_result.sharepro.txt</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Used in Fig. 4 main analysis; not directly in this table but cross-references the AD-SNP overlap calls</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>